--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_medianeta_a_2019.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_medianeta_a_2019.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:54</t>
+    <t xml:space="preserve">2026-09-24 00:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -600,10 +600,10 @@
         <v>13</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -614,10 +614,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10">
@@ -631,7 +631,7 @@
         <v>0.09</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -642,10 +642,10 @@
         <v>13</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12">

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_medianeta_a_2019.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_medianeta_a_2019.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:45</t>
+    <t xml:space="preserve">2026-10-01 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_medianeta_a_2019.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_medianeta_a_2019.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:04</t>
+    <t xml:space="preserve">2026-10-05 19:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
